--- a/Codes/Table3_DesireIndex.xlsx
+++ b/Codes/Table3_DesireIndex.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">Trait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h²</t>
   </si>
   <si>
     <t xml:space="preserve">Xo</t>
@@ -401,142 +404,163 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="C2" t="n">
         <v>748.71</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>783.05</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>34.34</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>4.59</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>12.35</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="C3" t="n">
         <v>32.18</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>33.69</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1.51</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>4.69</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>1.22</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>3.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="C4" t="n">
         <v>43.62</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>45.99</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>2.37</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>5.44</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1.91</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>4.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="C5" t="n">
         <v>87.77</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>88.79</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>1.01</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1.15</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.48</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C6" t="n">
         <v>42.52</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>42.79</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.26</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.62</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.06</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C7" t="n">
         <v>575.16</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>593.72</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>18.56</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>3.23</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>6.24</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1.09</v>
       </c>
     </row>
